--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -27783,12 +27783,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27822,81 +27822,100 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="O161" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="R161" t="n">
-        <v>0.06560937324041893</v>
+        <v>0.700866032121251</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27923,17 +27942,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27958,7 +27977,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -27967,81 +27986,175 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Cryptosporidiuminfektion</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28103,7 +28216,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -28112,13 +28225,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="O163" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="R163" t="n">
-        <v>0.0535762130827875</v>
+        <v>0.06560937324041893</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -28248,7 +28361,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -28393,7 +28506,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -28402,13 +28515,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="O165" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="R165" t="n">
-        <v>0.05558173977572607</v>
+        <v>0.0535762130827875</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -28538,7 +28651,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28683,7 +28796,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28692,13 +28805,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="O167" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="R167" t="n">
-        <v>0.06073880841471097</v>
+        <v>0.05558173977572607</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -28828,7 +28941,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -28973,7 +29086,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28982,13 +29095,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="O169" t="n">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="R169" t="n">
-        <v>0.04125654911187915</v>
+        <v>0.06073880841471097</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -29088,12 +29201,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -29118,22 +29231,22 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>0.007345623639039581</v>
+        <v>0</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -29166,42 +29279,42 @@
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29233,12 +29346,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -29263,109 +29376,90 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N171" t="n">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="O171" t="n">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="R171" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.04125654911187915</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29392,17 +29486,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -29436,175 +29530,81 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O172" t="n">
-        <v>4</v>
-      </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN172" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP172" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AT172" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV172" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29636,12 +29636,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -29675,13 +29675,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O173" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R173" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -29710,7 +29710,7 @@
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
@@ -29720,7 +29720,7 @@
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT173" t="n">
@@ -29728,47 +29728,47 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29800,12 +29800,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -29839,29 +29839,29 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O174" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -29921,17 +29921,17 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -29949,7 +29949,7 @@
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
@@ -29959,7 +29959,7 @@
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT174" t="n">
@@ -29967,45 +29967,448 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>7</v>
+      </c>
+      <c r="O175" t="n">
+        <v>7</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.1238283078056854</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV174" t="inlineStr">
+      <c r="AV175" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW174" t="inlineStr">
+      <c r="AW175" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX174" t="inlineStr">
+      <c r="AX175" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY174" t="inlineStr">
+      <c r="AY175" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ174" t="inlineStr">
+      <c r="AZ175" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA174" t="inlineStr">
+      <c r="BA175" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB174" t="inlineStr">
+      <c r="BB175" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC174" t="inlineStr">
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>7</v>
+      </c>
+      <c r="O176" t="n">
+        <v>7</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Cryptosporidose</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN176" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -30127,7 +30530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -30137,7 +30540,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -30157,7 +30560,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -30189,7 +30592,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7067</v>
+        <v>7154</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -21831,13 +21831,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O124" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="R124" t="n">
-        <v>0.5876498911231663</v>
+        <v>0.5913227029426862</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -25877,13 +25877,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="O149" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="R149" t="n">
-        <v>0.5325577138303695</v>
+        <v>0.5472489611084488</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -27016,13 +27016,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O157" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R157" t="n">
-        <v>1.42304733669131</v>
+        <v>1.440835428399951</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -27180,10 +27180,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O158" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -29491,12 +29491,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -29521,22 +29521,22 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R172" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -29569,42 +29569,42 @@
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29636,12 +29636,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -29675,100 +29675,81 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O173" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="R173" t="n">
-        <v>0.284609467338262</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29795,7 +29776,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -29839,103 +29820,28 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O174" t="n">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.3379737424641861</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN174" t="b">
-        <v>1</v>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
@@ -30034,17 +29940,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -30078,22 +29984,39 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="O175" t="n">
-        <v>7</v>
-      </c>
-      <c r="R175" t="n">
-        <v>0.1238283078056854</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>19</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1270</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -30101,6 +30024,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -30113,7 +30094,7 @@
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
@@ -30123,7 +30104,7 @@
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT175" t="n">
@@ -30131,47 +30112,47 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30179,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -30247,98 +30228,23 @@
       <c r="O176" t="n">
         <v>7</v>
       </c>
+      <c r="R176" t="n">
+        <v>0.1238283078056854</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>Cryptosporidose</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE176" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF176" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN176" t="b">
-        <v>1</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
@@ -30409,6 +30315,245 @@
         </is>
       </c>
       <c r="BC176" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>7</v>
+      </c>
+      <c r="O177" t="n">
+        <v>7</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Cryptosporidose</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -30530,7 +30675,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
@@ -30540,7 +30685,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -30592,7 +30737,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7154</v>
+        <v>7164</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -25877,13 +25877,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O149" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R149" t="n">
-        <v>0.5472489611084488</v>
+        <v>0.5509217729279685</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -27419,13 +27419,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="O159" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="R159" t="n">
-        <v>2.511945672629619</v>
+        <v>2.565014947403484</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27583,10 +27583,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="O160" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -29820,13 +29820,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O174" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R174" t="n">
-        <v>0.3379737424641861</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -29984,10 +29984,10 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O175" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
@@ -30223,13 +30223,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="O176" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="R176" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.6014517807704721</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -30387,10 +30387,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="O177" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7164</v>
+        <v>7198</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -25877,13 +25877,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="O149" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="R149" t="n">
-        <v>0.5509217729279685</v>
+        <v>0.5656130202060476</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -29820,13 +29820,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O174" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R174" t="n">
-        <v>0.3913380175901103</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -29984,10 +29984,10 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O175" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
@@ -30556,6 +30556,151 @@
       <c r="BC177" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>143</v>
+      </c>
+      <c r="O178" t="n">
+        <v>143</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.04097004529860222</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30592,7 +30737,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -30675,7 +30820,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -30685,7 +30830,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -30737,7 +30882,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7198</v>
+        <v>7347</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -11034,10 +11034,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O61" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -11190,10 +11190,10 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O62" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -14355,10 +14355,10 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O80" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -14511,10 +14511,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O81" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -18679,10 +18679,10 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O106" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -18835,10 +18835,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O107" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22970,22 +22970,19 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>37</v>
+        <v>167</v>
       </c>
       <c r="O132" t="n">
-        <v>37</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0.6581593932197309</v>
+        <v>167</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -23000,70 +22997,65 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23095,12 +23087,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23134,24 +23126,24 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>37</v>
+        <v>167</v>
       </c>
       <c r="O133" t="n">
-        <v>37</v>
+        <v>167</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
@@ -23166,7 +23158,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -23181,7 +23173,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -23216,17 +23208,17 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
+          <t>PHO IDTO current-year monthly preliminary cryptosporidiosis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -23239,70 +23231,65 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23334,12 +23321,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23373,13 +23360,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O134" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R134" t="n">
-        <v>0.7252800885761576</v>
+        <v>0.6581593932197309</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23388,7 +23375,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -23408,7 +23395,7 @@
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
@@ -23418,7 +23405,7 @@
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -23426,47 +23413,47 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23498,12 +23485,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23537,29 +23524,29 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O135" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -23584,7 +23571,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -23619,17 +23606,17 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -23647,7 +23634,7 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
@@ -23657,7 +23644,7 @@
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -23665,47 +23652,47 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23737,12 +23724,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23776,13 +23763,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="O136" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="R136" t="n">
-        <v>0.5484655352768304</v>
+        <v>0.7252800885761576</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23791,7 +23778,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -23806,7 +23793,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -23814,57 +23801,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23896,12 +23888,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23935,29 +23927,29 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="O137" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Cryptosporidose</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -23967,7 +23959,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -23982,7 +23974,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -24017,17 +24009,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly cryptosporidiosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -24040,7 +24032,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -24048,57 +24040,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24130,12 +24127,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24169,13 +24166,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="O138" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="R138" t="n">
-        <v>0.5793825865535674</v>
+        <v>0.5484655352768304</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24184,7 +24181,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -24199,7 +24196,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -24207,62 +24204,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24294,12 +24286,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -24333,29 +24325,29 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="O139" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>Cryptosporidiuminfektion</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -24365,7 +24357,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -24380,7 +24372,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -24415,17 +24407,17 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly cryptosporidiosis notifications.</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -24438,7 +24430,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
@@ -24446,62 +24438,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24533,12 +24520,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24563,7 +24550,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24572,81 +24559,100 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>0.5793825865535674</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24673,17 +24679,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24708,7 +24714,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24717,81 +24723,175 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="O141" t="n">
-        <v>91</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0.0260718470082014</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Cryptosporidiuminfektion</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24853,7 +24953,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24998,7 +25098,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -25007,13 +25107,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="O143" t="n">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="R143" t="n">
-        <v>0.04498109868447935</v>
+        <v>0.0260718470082014</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -25143,7 +25243,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -25288,7 +25388,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25297,13 +25397,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>216</v>
+        <v>157</v>
       </c>
       <c r="O145" t="n">
-        <v>216</v>
+        <v>157</v>
       </c>
       <c r="R145" t="n">
-        <v>0.06188482366781873</v>
+        <v>0.04498109868447935</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25433,7 +25533,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25578,7 +25678,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25587,13 +25687,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="O147" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0647498618005881</v>
+        <v>0.06188482366781873</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25723,7 +25823,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25838,12 +25938,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25868,22 +25968,22 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>154</v>
+        <v>226</v>
       </c>
       <c r="O149" t="n">
-        <v>154</v>
+        <v>226</v>
       </c>
       <c r="R149" t="n">
-        <v>0.5656130202060476</v>
+        <v>0.0647498618005881</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25916,42 +26016,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25983,12 +26083,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -26013,23 +26113,26 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -26058,42 +26161,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26125,12 +26228,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -26164,14 +26267,17 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>154</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0.5656130202060476</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -26205,12 +26311,12 @@
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -26225,12 +26331,12 @@
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
@@ -26267,12 +26373,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26306,10 +26412,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="O152" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26347,7 +26453,7 @@
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
@@ -26367,7 +26473,7 @@
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
@@ -26409,12 +26515,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26448,10 +26554,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26489,7 +26595,7 @@
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
@@ -26509,7 +26615,7 @@
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
@@ -26551,12 +26657,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26590,10 +26696,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26631,7 +26737,7 @@
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
@@ -26651,7 +26757,7 @@
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
@@ -26693,12 +26799,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26732,10 +26838,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="O155" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26773,7 +26879,7 @@
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
@@ -26793,7 +26899,7 @@
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
@@ -26835,12 +26941,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26874,10 +26980,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26915,7 +27021,7 @@
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
@@ -26935,7 +27041,7 @@
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
@@ -26977,12 +27083,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -27016,100 +27122,78 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="O157" t="n">
-        <v>81</v>
-      </c>
-      <c r="R157" t="n">
-        <v>1.440835428399951</v>
+        <v>43</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27136,17 +27220,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27180,175 +27264,78 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="O158" t="n">
-        <v>81</v>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP158" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AT158" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV158" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27380,12 +27367,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27419,13 +27406,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="O159" t="n">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="R159" t="n">
-        <v>2.565014947403484</v>
+        <v>1.440835428399951</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27434,7 +27421,7 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -27454,7 +27441,7 @@
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
@@ -27464,7 +27451,7 @@
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT159" t="n">
@@ -27472,47 +27459,47 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27544,12 +27531,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27583,29 +27570,29 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="O160" t="n">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
@@ -27630,7 +27617,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -27665,17 +27652,17 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -27693,7 +27680,7 @@
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
@@ -27703,7 +27690,7 @@
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT160" t="n">
@@ -27711,47 +27698,47 @@
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27783,12 +27770,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27822,13 +27809,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="O161" t="n">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="R161" t="n">
-        <v>0.700866032121251</v>
+        <v>2.565014947403484</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27837,7 +27824,7 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -27867,7 +27854,7 @@
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT161" t="n">
@@ -27880,42 +27867,42 @@
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27947,12 +27934,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27986,29 +27973,29 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="O162" t="n">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>Cryptosporidiuminfektion</t>
+          <t>Cryptosporidose</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
@@ -28033,7 +28020,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -28068,17 +28055,17 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -28106,7 +28093,7 @@
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT162" t="n">
@@ -28119,42 +28106,42 @@
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28186,12 +28173,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28225,81 +28212,100 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="O163" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="R163" t="n">
-        <v>0.06560937324041893</v>
+        <v>0.700866032121251</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28326,17 +28332,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28361,7 +28367,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -28370,81 +28376,175 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O164" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Cryptosporidiuminfektion</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28506,7 +28606,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -28515,13 +28615,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="O165" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="R165" t="n">
-        <v>0.0535762130827875</v>
+        <v>0.06560937324041893</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -28651,7 +28751,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28796,7 +28896,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28805,13 +28905,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="O167" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="R167" t="n">
-        <v>0.05558173977572607</v>
+        <v>0.0535762130827875</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -28941,7 +29041,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -29086,7 +29186,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -29095,13 +29195,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="O169" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="R169" t="n">
-        <v>0.06073880841471097</v>
+        <v>0.05558173977572607</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -29231,7 +29331,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -29376,7 +29476,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -29385,13 +29485,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="O171" t="n">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="R171" t="n">
-        <v>0.04125654911187915</v>
+        <v>0.06073880841471097</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -29521,7 +29621,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -29530,13 +29630,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -29636,12 +29736,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -29666,22 +29766,22 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="O173" t="n">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="R173" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.04125654911187915</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -29714,42 +29814,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29781,12 +29881,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -29811,109 +29911,90 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="O174" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="R174" t="n">
-        <v>0.426914201007393</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29940,17 +30021,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -29984,175 +30065,81 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="O175" t="n">
-        <v>24</v>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN175" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP175" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AT175" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV175" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30184,12 +30171,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -30223,13 +30210,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O176" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="R176" t="n">
-        <v>0.6014517807704721</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -30238,7 +30225,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -30258,7 +30245,7 @@
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
@@ -30268,7 +30255,7 @@
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT176" t="n">
@@ -30276,47 +30263,47 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30348,12 +30335,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -30387,29 +30374,29 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O177" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
@@ -30434,7 +30421,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -30469,17 +30456,17 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -30497,7 +30484,7 @@
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
@@ -30507,7 +30494,7 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT177" t="n">
@@ -30515,47 +30502,47 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30587,118 +30574,521 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>34</v>
+      </c>
+      <c r="O178" t="n">
+        <v>34</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.6014517807704721</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>34</v>
+      </c>
+      <c r="O179" t="n">
+        <v>34</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Cryptosporidose</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>D096</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
         <is>
           <t>隐孢子虫病</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N178" t="n">
+      <c r="N180" t="n">
         <v>143</v>
       </c>
-      <c r="O178" t="n">
+      <c r="O180" t="n">
         <v>143</v>
       </c>
-      <c r="R178" t="n">
+      <c r="R180" t="n">
         <v>0.04097004529860222</v>
       </c>
-      <c r="S178" t="inlineStr">
+      <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO178" t="inlineStr">
+      <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP178" t="inlineStr">
+      <c r="AP180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR178" t="inlineStr">
+      <c r="AR180" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS178" t="inlineStr"/>
-      <c r="AT178" t="n">
+      <c r="AS180" t="inlineStr"/>
+      <c r="AT180" t="n">
         <v>0</v>
       </c>
-      <c r="AU178" t="inlineStr">
+      <c r="AU180" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV178" t="inlineStr">
+      <c r="AV180" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW178" t="inlineStr">
+      <c r="AW180" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX178" t="inlineStr">
+      <c r="AX180" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY178" t="inlineStr">
+      <c r="AY180" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ178" t="inlineStr">
+      <c r="AZ180" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA178" t="inlineStr">
+      <c r="BA180" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB178" t="inlineStr">
+      <c r="BB180" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC178" t="inlineStr">
+      <c r="BC180" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -30820,7 +31210,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -30830,7 +31220,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -30850,7 +31240,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -30882,7 +31272,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7347</v>
+        <v>7518</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -26267,13 +26267,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="O151" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="R151" t="n">
-        <v>0.5656130202060476</v>
+        <v>0.5803042674841269</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O176" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R176" t="n">
-        <v>0.426914201007393</v>
+        <v>0.4624903844246757</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -30374,10 +30374,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O177" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7518</v>
+        <v>7524</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -26267,13 +26267,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O151" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R151" t="n">
-        <v>0.5803042674841269</v>
+        <v>0.5839770793036466</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7524</v>
+        <v>7525</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O176" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R176" t="n">
-        <v>0.4624903844246757</v>
+        <v>0.5336427512592412</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -30374,10 +30374,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O177" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -31091,6 +31091,151 @@
       <c r="BC180" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
+      <c r="AT181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31272,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -31210,7 +31355,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
@@ -31220,7 +31365,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -31272,7 +31417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7525</v>
+        <v>7529</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -28173,12 +28173,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28212,13 +28212,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O163" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R163" t="n">
-        <v>0.700866032121251</v>
+        <v>1.43735795451859</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -28242,7 +28242,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
@@ -28250,62 +28250,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28337,12 +28332,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28376,29 +28371,29 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O164" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>Cryptosporidiuminfektion</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
@@ -28408,7 +28403,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -28423,7 +28418,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -28458,17 +28453,17 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly cryptosporidiosis notifications.</t>
         </is>
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -28481,7 +28476,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ164" t="inlineStr">
@@ -28489,62 +28484,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28576,12 +28566,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28615,81 +28605,100 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="O165" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="R165" t="n">
-        <v>0.06560937324041893</v>
+        <v>0.700866032121251</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR165" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28716,17 +28725,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28751,7 +28760,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28760,81 +28769,175 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Cryptosporidiuminfektion</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28896,7 +28999,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28905,13 +29008,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="O167" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="R167" t="n">
-        <v>0.0535762130827875</v>
+        <v>0.06560937324041893</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -29041,7 +29144,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -29186,7 +29289,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -29195,13 +29298,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="O169" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="R169" t="n">
-        <v>0.05558173977572607</v>
+        <v>0.0535762130827875</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -29331,7 +29434,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -29476,7 +29579,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -29485,13 +29588,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="O171" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="R171" t="n">
-        <v>0.06073880841471097</v>
+        <v>0.05558173977572607</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -29621,7 +29724,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -29766,7 +29869,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -29775,13 +29878,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="O173" t="n">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="R173" t="n">
-        <v>0.04125654911187915</v>
+        <v>0.06073880841471097</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -29911,7 +30014,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29920,13 +30023,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -30026,12 +30129,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -30056,22 +30159,22 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="O175" t="n">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="R175" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.04125654911187915</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -30104,42 +30207,42 @@
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30171,12 +30274,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -30201,109 +30304,90 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O176" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R176" t="n">
-        <v>0.5336427512592412</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30330,17 +30414,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -30374,175 +30458,81 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O177" t="n">
-        <v>30</v>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE177" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN177" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP177" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AT177" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV177" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30574,12 +30564,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -30613,13 +30603,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O178" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R178" t="n">
-        <v>0.6014517807704721</v>
+        <v>0.5336427512592412</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -30628,7 +30618,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -30648,7 +30638,7 @@
       </c>
       <c r="AQ178" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR178" t="inlineStr">
@@ -30658,7 +30648,7 @@
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT178" t="n">
@@ -30666,47 +30656,47 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30738,12 +30728,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -30777,29 +30767,29 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O179" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr">
@@ -30824,7 +30814,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -30859,17 +30849,17 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -30887,7 +30877,7 @@
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
@@ -30897,7 +30887,7 @@
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT179" t="n">
@@ -30905,47 +30895,47 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30977,12 +30967,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -31007,7 +30997,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -31016,81 +31006,100 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="O180" t="n">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="R180" t="n">
-        <v>0.04097004529860222</v>
+        <v>0.6014517807704721</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -31117,123 +31126,507 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>34</v>
+      </c>
+      <c r="O181" t="n">
+        <v>34</v>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Cryptosporidose</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN181" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>143</v>
+      </c>
+      <c r="O182" t="n">
+        <v>143</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0.04097004529860222</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
+      <c r="AT182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>D096</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
         <is>
           <t>隐孢子虫病</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="K183" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N181" t="n">
+      <c r="N183" t="n">
         <v>0</v>
       </c>
-      <c r="O181" t="n">
+      <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="R181" t="n">
+      <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S181" t="inlineStr">
+      <c r="S183" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO181" t="inlineStr">
+      <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP181" t="inlineStr">
+      <c r="AP183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR181" t="inlineStr">
+      <c r="AR183" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS181" t="inlineStr"/>
-      <c r="AT181" t="n">
+      <c r="AS183" t="inlineStr"/>
+      <c r="AT183" t="n">
         <v>0</v>
       </c>
-      <c r="AU181" t="inlineStr">
+      <c r="AU183" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV181" t="inlineStr">
+      <c r="AV183" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW181" t="inlineStr">
+      <c r="AW183" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX181" t="inlineStr">
+      <c r="AX183" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY181" t="inlineStr">
+      <c r="AY183" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ181" t="inlineStr">
+      <c r="AZ183" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA181" t="inlineStr">
+      <c r="BA183" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB181" t="inlineStr">
+      <c r="BB183" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC181" t="inlineStr">
+      <c r="BC183" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -31355,7 +31748,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
@@ -31365,7 +31758,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -31385,7 +31778,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -31417,7 +31810,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7529</v>
+        <v>7605</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -31006,13 +31006,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O180" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="R180" t="n">
-        <v>0.6014517807704721</v>
+        <v>0.9198674294136632</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -31170,10 +31170,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O181" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7605</v>
+        <v>7623</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -30603,13 +30603,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="O178" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R178" t="n">
-        <v>0.5336427512592412</v>
+        <v>0.6403713015110895</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -30767,10 +30767,10 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="O179" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7623</v>
+        <v>7629</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -26267,13 +26267,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="O151" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="R151" t="n">
-        <v>0.5839770793036466</v>
+        <v>0.5986683265817258</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -31629,6 +31629,151 @@
       <c r="BC183" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>350</v>
+      </c>
+      <c r="O184" t="n">
+        <v>350</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0.1002763346469285</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
+      <c r="AT184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV184" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31665,7 +31810,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -31748,7 +31893,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
@@ -31758,7 +31903,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -31810,7 +31955,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7629</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -26267,13 +26267,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O151" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R151" t="n">
-        <v>0.5986683265817258</v>
+        <v>0.6060139502207653</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7983</v>
+        <v>7985</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -26267,13 +26267,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="O151" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="R151" t="n">
-        <v>0.6060139502207653</v>
+        <v>0.6207051974988445</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -30603,13 +30603,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="O178" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="R178" t="n">
-        <v>0.6403713015110895</v>
+        <v>0.8894045854320688</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -30767,10 +30767,10 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="O179" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
@@ -31006,13 +31006,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="O180" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="R180" t="n">
-        <v>0.9198674294136632</v>
+        <v>1.185213803282989</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -31170,10 +31170,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="O181" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
@@ -31772,6 +31772,296 @@
         </is>
       </c>
       <c r="BC184" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
+      <c r="AT185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV185" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>174</v>
+      </c>
+      <c r="O186" t="n">
+        <v>174</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0.04985166351018731</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
+      <c r="AT186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -31810,7 +32100,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -31893,7 +32183,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
@@ -31903,7 +32193,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -31955,7 +32245,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7985</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -26267,13 +26267,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O151" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R151" t="n">
-        <v>0.6207051974988445</v>
+        <v>0.6243780093183643</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -30458,13 +30458,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>181</v>
       </c>
       <c r="O177" t="n">
-        <v>2</v>
+        <v>181</v>
       </c>
       <c r="R177" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.664778939333082</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -30603,13 +30603,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O178" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="R178" t="n">
-        <v>0.8894045854320688</v>
+        <v>1.174014052770331</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -30767,10 +30767,10 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O179" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
@@ -32064,6 +32064,699 @@
       <c r="BC186" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
+      <c r="AT187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV187" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>126</v>
+      </c>
+      <c r="O188" t="n">
+        <v>126</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0.03609948047289425</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr"/>
+      <c r="AT188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV188" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1270</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1270</t>
+        </is>
+      </c>
+      <c r="AT189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1270</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1270</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN190" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1270</t>
+        </is>
+      </c>
+      <c r="AT190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -32100,7 +32793,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -32183,7 +32876,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -32193,7 +32886,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -32213,7 +32906,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -32245,7 +32938,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8192</v>
+        <v>8514</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -30458,13 +30458,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="O177" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="R177" t="n">
-        <v>0.664778939333082</v>
+        <v>0.6868158102502008</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8514</v>
+        <v>8520</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -15404,7 +15404,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -31006,13 +31006,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O180" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="R180" t="n">
-        <v>1.185213803282989</v>
+        <v>1.379801144120495</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -31170,10 +31170,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O181" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -32938,7 +32938,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8520</v>
+        <v>8531</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1202,6 +1217,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1347,6 +1367,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1492,6 +1517,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1628,6 +1658,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1773,6 +1808,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1918,6 +1958,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2050,10 +2095,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -2206,10 +2251,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3099,7 +3144,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4061,6 +4106,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4357,6 +4407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4653,6 +4708,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4949,6 +5009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5245,6 +5310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5393,6 +5463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5529,6 +5604,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5674,6 +5754,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5819,6 +5904,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5964,6 +6054,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6109,6 +6204,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6254,6 +6354,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6399,6 +6504,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6544,6 +6654,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6676,10 +6791,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O39" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -6832,10 +6947,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O40" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -7725,7 +7840,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -8835,6 +8950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9131,6 +9251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9427,6 +9552,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9723,6 +9853,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9871,6 +10006,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10007,6 +10147,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10152,6 +10297,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10288,6 +10438,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10433,6 +10588,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10578,6 +10738,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10714,6 +10879,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10859,6 +11029,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11004,6 +11179,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12185,7 +12365,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -13295,6 +13475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13591,6 +13776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13887,6 +14077,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14183,6 +14378,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14328,6 +14528,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14464,6 +14669,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14609,6 +14819,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14745,6 +14960,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14890,6 +15110,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15035,6 +15260,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15171,6 +15401,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15316,6 +15551,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15461,6 +15701,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16642,7 +16887,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -17749,6 +17994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18045,6 +18295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18341,6 +18596,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18637,6 +18897,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18782,6 +19047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18918,6 +19188,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19063,6 +19338,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19208,6 +19488,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19353,6 +19638,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19498,6 +19788,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19643,6 +19938,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19788,6 +20088,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19933,6 +20238,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20065,10 +20375,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O120" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20221,10 +20531,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O121" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -21114,7 +21424,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -22221,6 +22531,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22517,6 +22832,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22813,6 +23133,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23109,6 +23434,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23402,6 +23732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23547,6 +23882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23683,6 +24023,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23828,6 +24173,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23964,6 +24314,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24109,6 +24464,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24254,6 +24614,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24390,6 +24755,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24535,6 +24905,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24680,6 +25055,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25861,7 +26241,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -26962,6 +27342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27252,6 +27637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27542,6 +27932,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27832,6 +28227,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27977,6 +28377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28113,6 +28518,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28258,6 +28668,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28403,6 +28818,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28548,6 +28968,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28693,6 +29118,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28838,6 +29268,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28983,6 +29418,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29128,6 +29568,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29260,10 +29705,10 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="O176" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29416,10 +29861,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="O177" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -30309,7 +30754,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -31410,6 +31855,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31700,6 +32150,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31990,6 +32445,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32280,6 +32740,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32557,17 +33022,22 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O195" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R195" t="n">
-        <v>0.6243780093183643</v>
+        <v>0.6280508211378841</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -32706,6 +33176,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32851,6 +33326,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32996,6 +33476,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33141,6 +33626,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33286,6 +33776,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33431,6 +33926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33576,6 +34076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33721,6 +34226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33814,12 +34324,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -33853,22 +34363,19 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="O204" t="n">
-        <v>81</v>
-      </c>
-      <c r="R204" t="n">
-        <v>1.440835428399951</v>
+        <v>142</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -33883,70 +34390,65 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -33978,12 +34480,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -34017,24 +34519,24 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="O205" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X205" t="inlineStr">
@@ -34049,7 +34551,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -34064,7 +34566,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -34099,17 +34601,17 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
+          <t>PHO IDTO current-year monthly preliminary cryptosporidiosis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -34122,70 +34624,65 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -34217,12 +34714,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -34256,13 +34753,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="O206" t="n">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="R206" t="n">
-        <v>2.565014947403484</v>
+        <v>1.440835428399951</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -34271,7 +34768,7 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -34291,7 +34788,7 @@
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
@@ -34301,7 +34798,7 @@
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT206" t="n">
@@ -34309,47 +34806,47 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34381,12 +34878,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -34420,29 +34917,29 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="O207" t="n">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
@@ -34467,7 +34964,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -34502,17 +34999,17 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -34530,7 +35027,7 @@
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -34540,7 +35037,7 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT207" t="n">
@@ -34548,47 +35045,47 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34620,12 +35117,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -34659,13 +35156,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="O208" t="n">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="R208" t="n">
-        <v>1.43735795451859</v>
+        <v>2.565014947403484</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -34674,7 +35171,7 @@
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -34689,7 +35186,7 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
@@ -34697,57 +35194,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34779,12 +35281,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -34818,29 +35320,29 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="O209" t="n">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Cryptosporidose</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr">
@@ -34850,7 +35352,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -34865,7 +35367,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
@@ -34900,17 +35402,17 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly cryptosporidiosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -34923,7 +35425,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
@@ -34931,57 +35433,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -35013,12 +35520,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -35052,13 +35559,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O210" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R210" t="n">
-        <v>0.700866032121251</v>
+        <v>1.43735795451859</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -35067,7 +35574,7 @@
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -35082,7 +35589,7 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
@@ -35090,62 +35597,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35177,12 +35679,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -35216,29 +35718,29 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O211" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>Cryptosporidiuminfektion</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
@@ -35248,7 +35750,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -35263,7 +35765,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -35298,17 +35800,17 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly cryptosporidiosis notifications.</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -35321,7 +35823,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
@@ -35329,62 +35831,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35416,12 +35913,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -35455,81 +35952,100 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="O212" t="n">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="R212" t="n">
-        <v>0.06560937324041893</v>
+        <v>0.700866032121251</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR212" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35556,17 +36072,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -35591,7 +36107,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -35600,81 +36116,175 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Cryptosporidiuminfektion</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR213" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35736,7 +36346,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -35745,17 +36355,22 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="O214" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="R214" t="n">
-        <v>0.0535762130827875</v>
+        <v>0.06560937324041893</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -35881,7 +36496,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -36026,7 +36641,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -36035,17 +36650,22 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="O216" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="R216" t="n">
-        <v>0.05558173977572607</v>
+        <v>0.0535762130827875</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -36171,7 +36791,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -36316,7 +36936,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -36325,17 +36945,22 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="O218" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="R218" t="n">
-        <v>0.06073880841471097</v>
+        <v>0.05558173977572607</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -36461,7 +37086,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -36606,7 +37231,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -36615,17 +37240,22 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="O220" t="n">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="R220" t="n">
-        <v>0.04125654911187915</v>
+        <v>0.06073880841471097</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -36751,7 +37381,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -36760,13 +37390,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -36866,12 +37496,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -36896,26 +37526,31 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N222" t="n">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="O222" t="n">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="R222" t="n">
-        <v>0.7051798693477997</v>
+        <v>0.04125654911187915</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -36944,42 +37579,42 @@
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37011,12 +37646,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -37041,26 +37676,26 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -37089,42 +37724,42 @@
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37156,12 +37791,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -37195,17 +37830,22 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>46</v>
+        <v>197</v>
       </c>
       <c r="O224" t="n">
-        <v>46</v>
+        <v>197</v>
       </c>
       <c r="R224" t="n">
-        <v>0.5305587417914777</v>
+        <v>0.7235439284453987</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -37239,12 +37879,12 @@
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -37259,12 +37899,12 @@
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
@@ -37301,12 +37941,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -37339,9 +37979,23 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -37375,7 +38029,7 @@
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
@@ -37395,7 +38049,7 @@
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
@@ -37437,12 +38091,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -37476,17 +38130,22 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="O226" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R226" t="n">
-        <v>0.6446598382670429</v>
+        <v>0.5305587417914777</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -37520,7 +38179,7 @@
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
@@ -37540,7 +38199,7 @@
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
@@ -37582,12 +38241,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -37620,18 +38279,14 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N227" t="n">
-        <v>27</v>
-      </c>
-      <c r="O227" t="n">
-        <v>27</v>
-      </c>
-      <c r="R227" t="n">
-        <v>1.4085712079698</v>
-      </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -37665,7 +38320,7 @@
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
@@ -37685,7 +38340,7 @@
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
@@ -37727,12 +38382,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -37766,17 +38421,22 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="O228" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="R228" t="n">
-        <v>1.549877645770298</v>
+        <v>0.6446598382670429</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -37810,7 +38470,7 @@
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
@@ -37830,7 +38490,7 @@
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
@@ -37872,12 +38532,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -37911,17 +38571,22 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="O229" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="R229" t="n">
-        <v>0.7268436353867178</v>
+        <v>1.4085712079698</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -37955,7 +38620,7 @@
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
@@ -37975,7 +38640,7 @@
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
@@ -38017,12 +38682,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -38056,17 +38721,22 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O230" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R230" t="n">
-        <v>0.4844613855208057</v>
+        <v>1.549877645770298</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -38100,7 +38770,7 @@
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
@@ -38120,7 +38790,7 @@
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
@@ -38162,12 +38832,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -38201,22 +38871,17 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="O231" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="R231" t="n">
-        <v>1.174014052770331</v>
+        <v>0.7268436353867178</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -38226,75 +38891,66 @@
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ231" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38321,17 +38977,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -38365,39 +39021,17 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="O232" t="n">
-        <v>66</v>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>15</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.4844613855208057</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -38405,135 +39039,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
+      <c r="AT232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO232" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP232" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AT232" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU232" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV232" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38565,12 +39132,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -38604,13 +39171,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="O233" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="R233" t="n">
-        <v>1.379801144120495</v>
+        <v>1.245166419604896</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -38619,7 +39186,7 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -38639,7 +39206,7 @@
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
@@ -38649,7 +39216,7 @@
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT233" t="n">
@@ -38657,47 +39224,47 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38729,12 +39296,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -38768,29 +39335,29 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="O234" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
@@ -38815,7 +39382,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
@@ -38850,17 +39417,17 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -38878,7 +39445,7 @@
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
@@ -38888,7 +39455,7 @@
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT234" t="n">
@@ -38896,47 +39463,47 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38968,12 +39535,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -38998,7 +39565,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -39007,81 +39574,100 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="O235" t="n">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="R235" t="n">
-        <v>0.04097004529860222</v>
+        <v>1.521319210184135</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -39108,17 +39694,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -39143,7 +39729,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -39152,81 +39738,175 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="O236" t="n">
-        <v>0</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0</v>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>86</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Cryptosporidose</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>1</v>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -39258,12 +39938,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -39288,7 +39968,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -39297,81 +39977,100 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>350</v>
+        <v>41</v>
       </c>
       <c r="O237" t="n">
-        <v>350</v>
+        <v>41</v>
       </c>
       <c r="R237" t="n">
-        <v>0.1002763346469285</v>
+        <v>0.3831400975596171</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39398,17 +40097,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -39433,7 +40132,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -39442,81 +40141,175 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Cryptosporidiuminfektion</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN238" t="b">
+        <v>1</v>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39578,7 +40371,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -39587,17 +40380,22 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="O239" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="R239" t="n">
-        <v>0.04985166351018731</v>
+        <v>0.04097004529860222</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
@@ -39723,7 +40521,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -39868,7 +40666,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -39877,17 +40675,22 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>126</v>
+        <v>350</v>
       </c>
       <c r="O241" t="n">
-        <v>126</v>
+        <v>350</v>
       </c>
       <c r="R241" t="n">
-        <v>0.03609948047289425</v>
+        <v>0.1002763346469285</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -40013,7 +40816,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -40128,12 +40931,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -40158,109 +40961,95 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N243" t="n">
+        <v>174</v>
+      </c>
+      <c r="O243" t="n">
+        <v>174</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0.04985166351018731</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="n">
         <v>0</v>
       </c>
-      <c r="O243" t="n">
-        <v>0</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO243" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP243" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ243" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AT243" t="n">
-        <v>2</v>
-      </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40287,17 +41076,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -40322,12 +41111,12 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N244" t="n">
@@ -40336,170 +41125,1327 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
+      <c r="AT244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>126</v>
+      </c>
+      <c r="O245" t="n">
+        <v>126</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0.03609948047289425</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr"/>
+      <c r="AT245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA245" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>8</v>
+      </c>
+      <c r="O247" t="n">
+        <v>8</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0.142304733669131</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
-      <c r="V244" t="inlineStr">
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
-      <c r="W244" t="inlineStr">
+      <c r="AT247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>8</v>
+      </c>
+      <c r="O248" t="n">
+        <v>8</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1270</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1270</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
         <is>
           <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z244" t="inlineStr">
+      <c r="Z248" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA244" t="inlineStr">
+      <c r="AA248" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB244" t="inlineStr">
+      <c r="AB248" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC244" t="inlineStr">
+      <c r="AC248" t="inlineStr">
         <is>
           <t>country:FI:national</t>
         </is>
       </c>
-      <c r="AD244" t="inlineStr">
+      <c r="AD248" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE244" t="inlineStr">
+      <c r="AE248" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF244" t="inlineStr">
+      <c r="AF248" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG244" t="inlineStr">
+      <c r="AG248" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH244" t="inlineStr">
+      <c r="AH248" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI244" t="inlineStr">
+      <c r="AI248" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ244" t="inlineStr">
+      <c r="AJ248" t="inlineStr">
         <is>
           <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
-      <c r="AK244" t="inlineStr">
+      <c r="AK248" t="inlineStr">
         <is>
           <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
-      <c r="AM244" t="inlineStr">
+      <c r="AM248" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN244" t="b">
+      <c r="AN248" t="b">
         <v>1</v>
       </c>
-      <c r="AO244" t="inlineStr">
+      <c r="AO248" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP244" t="inlineStr">
+      <c r="AP248" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ244" t="inlineStr">
+      <c r="AQ248" t="inlineStr">
         <is>
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR244" t="inlineStr">
+      <c r="AR248" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS244" t="inlineStr">
+      <c r="AS248" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
-      <c r="AT244" t="n">
+      <c r="AT248" t="n">
         <v>2</v>
       </c>
-      <c r="AU244" t="inlineStr">
+      <c r="AU248" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV244" t="inlineStr">
+      <c r="AV248" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW244" t="inlineStr">
+      <c r="AW248" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX244" t="inlineStr">
+      <c r="AX248" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY244" t="inlineStr">
+      <c r="AY248" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ244" t="inlineStr">
+      <c r="AZ248" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA244" t="inlineStr">
+      <c r="BA248" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB244" t="inlineStr">
+      <c r="BB248" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC244" t="inlineStr">
+      <c r="BC248" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>13</v>
+      </c>
+      <c r="O249" t="n">
+        <v>13</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0.2299668573534158</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV249" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA249" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB249" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC249" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N250" t="n">
+        <v>13</v>
+      </c>
+      <c r="O250" t="n">
+        <v>13</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Cryptosporidose</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV250" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA250" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB250" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>117</v>
+      </c>
+      <c r="O251" t="n">
+        <v>117</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.03352094615340181</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40536,7 +42482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -40619,7 +42565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -40629,7 +42575,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -40649,7 +42595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -40681,7 +42627,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9965</v>
+        <v>10313</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -37830,13 +37830,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O224" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="R224" t="n">
-        <v>0.7235439284453987</v>
+        <v>0.7272167402649184</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -39171,13 +39171,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O233" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R233" t="n">
-        <v>1.245166419604896</v>
+        <v>1.262954511313538</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -39335,10 +39335,10 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O234" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U234" t="inlineStr">
         <is>
@@ -41560,13 +41560,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O247" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R247" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -41724,10 +41724,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O248" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10313</v>
+        <v>10318</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -37830,13 +37830,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="O224" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="R224" t="n">
-        <v>0.7272167402649184</v>
+        <v>0.7455807993625174</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -41560,13 +41560,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O247" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R247" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -41724,10 +41724,10 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O248" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
@@ -41963,13 +41963,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O249" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R249" t="n">
-        <v>0.2299668573534158</v>
+        <v>0.3007258903852361</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -42127,10 +42127,10 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O250" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U250" t="inlineStr">
         <is>
@@ -42446,6 +42446,151 @@
       <c r="BC251" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
+      <c r="AT252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42482,7 +42627,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -42565,7 +42710,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -42575,7 +42720,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -42627,7 +42772,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10318</v>
+        <v>10334</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -4095,9 +4095,6 @@
       <c r="O21" t="n">
         <v>6</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -4396,9 +4393,6 @@
       <c r="O23" t="n">
         <v>59</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.01690372498333937</v>
       </c>
@@ -4697,9 +4691,6 @@
       <c r="O25" t="n">
         <v>69</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.01976876311610876</v>
       </c>
@@ -4998,9 +4989,6 @@
       <c r="O27" t="n">
         <v>69</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.01976876311610876</v>
       </c>
@@ -5299,9 +5287,6 @@
       <c r="O29" t="n">
         <v>59</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01690372498333937</v>
       </c>
@@ -8939,9 +8924,6 @@
       <c r="O50" t="n">
         <v>78</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.02234729743560121</v>
       </c>
@@ -9240,9 +9222,6 @@
       <c r="O52" t="n">
         <v>59</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.01690372498333937</v>
       </c>
@@ -9541,9 +9520,6 @@
       <c r="O54" t="n">
         <v>54</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.01547120591695468</v>
       </c>
@@ -9842,9 +9818,6 @@
       <c r="O56" t="n">
         <v>58</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.01661722117006243</v>
       </c>
@@ -13464,9 +13437,6 @@
       <c r="O77" t="n">
         <v>41</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.01174665634435448</v>
       </c>
@@ -13765,9 +13735,6 @@
       <c r="O79" t="n">
         <v>62</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.01776323642317019</v>
       </c>
@@ -14066,9 +14033,6 @@
       <c r="O81" t="n">
         <v>58</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.01661722117006243</v>
       </c>
@@ -14367,9 +14331,6 @@
       <c r="O83" t="n">
         <v>56</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.01604421354350856</v>
       </c>
@@ -17983,9 +17944,6 @@
       <c r="O104" t="n">
         <v>76</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.02177428980904733</v>
       </c>
@@ -18284,9 +18242,6 @@
       <c r="O106" t="n">
         <v>71</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.02034177074266263</v>
       </c>
@@ -18585,9 +18540,6 @@
       <c r="O108" t="n">
         <v>70</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.0200552669293857</v>
       </c>
@@ -18886,9 +18838,6 @@
       <c r="O110" t="n">
         <v>74</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.02120128218249345</v>
       </c>
@@ -22520,9 +22469,6 @@
       <c r="O131" t="n">
         <v>81</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.02320680887543202</v>
       </c>
@@ -22821,9 +22767,6 @@
       <c r="O133" t="n">
         <v>67</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.01919575548955488</v>
       </c>
@@ -23122,9 +23065,6 @@
       <c r="O135" t="n">
         <v>74</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.02120128218249345</v>
       </c>
@@ -23423,9 +23363,6 @@
       <c r="O137" t="n">
         <v>23</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.006589587705369587</v>
       </c>
@@ -42591,6 +42528,156 @@
       <c r="BC252" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>106</v>
+      </c>
+      <c r="O253" t="n">
+        <v>106</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0.03036940420735549</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV253" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA253" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42627,7 +42714,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -42710,7 +42797,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -42720,7 +42807,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -42772,7 +42859,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10334</v>
+        <v>10440</v>
       </c>
     </row>
     <row r="16">
